--- a/test/testdata/testdata2.xlsx
+++ b/test/testdata/testdata2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a2ae935e48e8e5e4/Develop/Public/kkzk/pdf-preview/test/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_AD4D066CA252ABDACC104883C1D6FFD072EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88BFEB3D-AFD4-4F9A-A45D-FCD04E960D31}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_AD4D066CA252ABDACC104883C1D6FFD072EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0938B558-645A-4017-A60F-D827AFBAC1FD}"/>
   <bookViews>
-    <workbookView xWindow="13020" yWindow="1937" windowWidth="11177" windowHeight="11014" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12257" yWindow="0" windowWidth="12514" windowHeight="15823" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,13 +75,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -97,10 +113,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -387,13 +399,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A2DBD3-EE1E-4577-9B5B-FDDAC8A93FCC}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18.45"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1">
+    <row r="1" spans="1:2">
+      <c r="A1" s="2">
         <v>12345</v>
       </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>12345</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>12345</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
